--- a/data/XHS.MI.xlsx
+++ b/data/XHS.MI.xlsx
@@ -19147,6 +19147,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="723">
+      <c r="A723" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B723" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C723" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D723" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E723" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F723" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G723" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="H723" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/XHS.MI.xlsx
+++ b/data/XHS.MI.xlsx
@@ -17001,6 +17001,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="724">
+      <c r="A724" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B724" t="n">
+        <v>0</v>
+      </c>
+      <c r="C724" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D724" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E724" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F724" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G724" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/XHS.MI.xlsx
+++ b/data/XHS.MI.xlsx
@@ -17116,6 +17116,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="729">
+      <c r="A729" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B729" t="n">
+        <v>0</v>
+      </c>
+      <c r="C729" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="D729" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="E729" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="F729" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="G729" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/XHS.MI.xlsx
+++ b/data/XHS.MI.xlsx
@@ -19381,6 +19381,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="732">
+      <c r="A732" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B732" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C732" t="n">
+        <v>2.57999992370605</v>
+      </c>
+      <c r="D732" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="E732" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="F732" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="G732" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="H732" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/XHS.MI.xlsx
+++ b/data/XHS.MI.xlsx
@@ -19459,6 +19459,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="735">
+      <c r="A735" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B735" t="n">
+        <v>11000</v>
+      </c>
+      <c r="C735" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="D735" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E735" t="n">
+        <v>2.61999988555908</v>
+      </c>
+      <c r="F735" t="n">
+        <v>2.57999992370605</v>
+      </c>
+      <c r="G735" t="n">
+        <v>2.57999992370605</v>
+      </c>
+      <c r="H735" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/XHS.MI.xlsx
+++ b/data/XHS.MI.xlsx
@@ -17339,8 +17339,31 @@
       <c r="E738" t="n">
         <v>2.27999997138977</v>
       </c>
-      <c r="F738"/>
+      <c r="F738" t="n">
+        <v>2.3199999332428</v>
+      </c>
       <c r="G738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B739" t="n">
+        <v>23000</v>
+      </c>
+      <c r="C739" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="D739" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E739" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="F739"/>
+      <c r="G739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/XHS.MI.xlsx
+++ b/data/XHS.MI.xlsx
@@ -17362,8 +17362,31 @@
       <c r="E739" t="n">
         <v>2.38000011444092</v>
       </c>
-      <c r="F739"/>
+      <c r="F739" t="n">
+        <v>2.27999997138977</v>
+      </c>
       <c r="G739" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B740" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C740" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="D740" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="E740" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="F740"/>
+      <c r="G740" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/XHS.MI.xlsx
+++ b/data/XHS.MI.xlsx
@@ -17385,8 +17385,31 @@
       <c r="E740" t="n">
         <v>2.24000000953674</v>
       </c>
-      <c r="F740"/>
+      <c r="F740" t="n">
+        <v>2.29999995231628</v>
+      </c>
       <c r="G740" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B741" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C741" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="D741" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="E741" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="F741"/>
+      <c r="G741" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/XHS.MI.xlsx
+++ b/data/XHS.MI.xlsx
@@ -17408,8 +17408,31 @@
       <c r="E741" t="n">
         <v>2.38000011444092</v>
       </c>
-      <c r="F741"/>
+      <c r="F741" t="n">
+        <v>2.35999989509583</v>
+      </c>
       <c r="G741" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B742" t="n">
+        <v>500</v>
+      </c>
+      <c r="C742" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="D742" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="E742" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="F742"/>
+      <c r="G742" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/XHS.MI.xlsx
+++ b/data/XHS.MI.xlsx
@@ -17438,6 +17438,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="743">
+      <c r="A743" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B743" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C743" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="D743" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="E743" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="F743" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="G743" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/XHS.MI.xlsx
+++ b/data/XHS.MI.xlsx
@@ -19745,6 +19745,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="746">
+      <c r="A746" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B746" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C746" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D746" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="E746" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F746" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="G746" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="H746" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/XHS.MI.xlsx
+++ b/data/XHS.MI.xlsx
@@ -19771,6 +19771,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="747">
+      <c r="A747" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B747" t="n">
+        <v>500</v>
+      </c>
+      <c r="C747" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="D747" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="E747" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="F747" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="G747" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="H747" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/XHS.MI.xlsx
+++ b/data/XHS.MI.xlsx
@@ -22041,6 +22041,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="748">
+      <c r="A748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B748" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C748" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="D748" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="E748" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="F748" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="G748" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="H748" t="n">
+        <v>0</v>
+      </c>
+      <c r="I748" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/XHS.MI.xlsx
+++ b/data/XHS.MI.xlsx
@@ -22070,6 +22070,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="749">
+      <c r="A749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B749" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C749" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="D749" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="E749" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="F749" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="G749" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="H749" t="n">
+        <v>0</v>
+      </c>
+      <c r="I749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B750" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C750" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="D750" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="E750" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="F750" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="G750" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="H750" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I750" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/XHS.MI.xlsx
+++ b/data/XHS.MI.xlsx
@@ -22128,6 +22128,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="751">
+      <c r="A751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B751" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C751" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="D751" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="E751" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="F751" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="G751" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="H751" t="n">
+        <v>5500</v>
+      </c>
+      <c r="I751" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/XHS.MI.xlsx
+++ b/data/XHS.MI.xlsx
@@ -22157,6 +22157,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="752">
+      <c r="A752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B752" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C752" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="D752" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="E752" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="F752" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="G752" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="H752" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I752" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/XHS.MI.xlsx
+++ b/data/XHS.MI.xlsx
@@ -22186,6 +22186,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="753">
+      <c r="A753" t="s">
+        <v>9</v>
+      </c>
+      <c r="B753" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C753" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="D753" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="E753" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="F753" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="G753" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="H753" t="n">
+        <v>500</v>
+      </c>
+      <c r="I753" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/XHS.MI.xlsx
+++ b/data/XHS.MI.xlsx
@@ -22215,6 +22215,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="754">
+      <c r="A754" t="s">
+        <v>9</v>
+      </c>
+      <c r="B754" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C754" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="D754" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="E754" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="F754" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="G754" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="H754" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I754" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/XHS.MI.xlsx
+++ b/data/XHS.MI.xlsx
@@ -22244,6 +22244,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="755">
+      <c r="A755" t="s">
+        <v>9</v>
+      </c>
+      <c r="B755" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C755" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="D755" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="E755" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="F755" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="G755" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="H755" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I755" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/XHS.MI.xlsx
+++ b/data/XHS.MI.xlsx
@@ -22273,6 +22273,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="756">
+      <c r="A756" t="s">
+        <v>9</v>
+      </c>
+      <c r="B756" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C756" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="D756" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="E756" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="F756" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="G756" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="H756" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I756" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/XHS.MI.xlsx
+++ b/data/XHS.MI.xlsx
@@ -22302,6 +22302,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="757">
+      <c r="A757" t="s">
+        <v>9</v>
+      </c>
+      <c r="B757" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C757" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="D757" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="E757" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="F757" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="G757" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="H757" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I757" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
